--- a/outputs/analysis/analysis_output/tables/part2/benefit_prevalence_over_time.xlsx
+++ b/outputs/analysis/analysis_output/tables/part2/benefit_prevalence_over_time.xlsx
@@ -649,13 +649,13 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>100</v>
+        <v>95.45454545454545</v>
       </c>
       <c r="F3" t="n">
         <v>100</v>
       </c>
       <c r="G3" t="n">
-        <v>8.333333333333332</v>
+        <v>31.81818181818182</v>
       </c>
     </row>
     <row r="4">
@@ -663,7 +663,7 @@
         <v>2010</v>
       </c>
       <c r="B4" t="n">
-        <v>100</v>
+        <v>97.72727272727273</v>
       </c>
       <c r="C4" t="n">
         <v>100</v>
@@ -672,13 +672,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>100</v>
+        <v>97.72727272727273</v>
       </c>
       <c r="F4" t="n">
         <v>100</v>
       </c>
       <c r="G4" t="n">
-        <v>19.23076923076923</v>
+        <v>18.18181818181818</v>
       </c>
     </row>
     <row r="5">
@@ -686,22 +686,22 @@
         <v>2011</v>
       </c>
       <c r="B5" t="n">
-        <v>100</v>
+        <v>98.83720930232558</v>
       </c>
       <c r="C5" t="n">
-        <v>100</v>
+        <v>98.83720930232558</v>
       </c>
       <c r="D5" t="n">
-        <v>100</v>
+        <v>98.83720930232558</v>
       </c>
       <c r="E5" t="n">
-        <v>100</v>
+        <v>98.83720930232558</v>
       </c>
       <c r="F5" t="n">
-        <v>100</v>
+        <v>98.83720930232558</v>
       </c>
       <c r="G5" t="n">
-        <v>28.26086956521739</v>
+        <v>32.55813953488372</v>
       </c>
     </row>
     <row r="6">
@@ -712,7 +712,7 @@
         <v>100</v>
       </c>
       <c r="C6" t="n">
-        <v>96.51162790697676</v>
+        <v>100</v>
       </c>
       <c r="D6" t="n">
         <v>100</v>
@@ -721,10 +721,10 @@
         <v>100</v>
       </c>
       <c r="F6" t="n">
-        <v>100</v>
+        <v>98.79518072289156</v>
       </c>
       <c r="G6" t="n">
-        <v>23.25581395348837</v>
+        <v>30.12048192771084</v>
       </c>
     </row>
     <row r="7">
@@ -732,22 +732,22 @@
         <v>2013</v>
       </c>
       <c r="B7" t="n">
-        <v>98.4126984126984</v>
+        <v>98.36065573770492</v>
       </c>
       <c r="C7" t="n">
-        <v>96.82539682539682</v>
+        <v>98.36065573770492</v>
       </c>
       <c r="D7" t="n">
-        <v>98.4126984126984</v>
+        <v>98.36065573770492</v>
       </c>
       <c r="E7" t="n">
         <v>100</v>
       </c>
       <c r="F7" t="n">
-        <v>98.4126984126984</v>
+        <v>98.36065573770492</v>
       </c>
       <c r="G7" t="n">
-        <v>28.57142857142857</v>
+        <v>32.78688524590164</v>
       </c>
     </row>
     <row r="8">
@@ -755,22 +755,22 @@
         <v>2014</v>
       </c>
       <c r="B8" t="n">
-        <v>99.05660377358491</v>
+        <v>98.01980198019803</v>
       </c>
       <c r="C8" t="n">
-        <v>98.11320754716981</v>
+        <v>99.00990099009901</v>
       </c>
       <c r="D8" t="n">
         <v>100</v>
       </c>
       <c r="E8" t="n">
-        <v>100</v>
+        <v>98.01980198019803</v>
       </c>
       <c r="F8" t="n">
-        <v>99.05660377358491</v>
+        <v>98.01980198019803</v>
       </c>
       <c r="G8" t="n">
-        <v>17.92452830188679</v>
+        <v>25.74257425742574</v>
       </c>
     </row>
     <row r="9">
@@ -778,22 +778,22 @@
         <v>2015</v>
       </c>
       <c r="B9" t="n">
-        <v>100</v>
+        <v>97.9381443298969</v>
       </c>
       <c r="C9" t="n">
-        <v>100</v>
+        <v>98.96907216494846</v>
       </c>
       <c r="D9" t="n">
-        <v>99.00990099009901</v>
+        <v>97.9381443298969</v>
       </c>
       <c r="E9" t="n">
-        <v>100</v>
+        <v>97.9381443298969</v>
       </c>
       <c r="F9" t="n">
-        <v>100</v>
+        <v>98.96907216494846</v>
       </c>
       <c r="G9" t="n">
-        <v>24.75247524752475</v>
+        <v>30.92783505154639</v>
       </c>
     </row>
     <row r="10">
@@ -801,22 +801,22 @@
         <v>2016</v>
       </c>
       <c r="B10" t="n">
-        <v>98.93617021276596</v>
+        <v>98.88888888888889</v>
       </c>
       <c r="C10" t="n">
-        <v>98.93617021276596</v>
+        <v>98.88888888888889</v>
       </c>
       <c r="D10" t="n">
-        <v>98.93617021276596</v>
+        <v>98.88888888888889</v>
       </c>
       <c r="E10" t="n">
-        <v>98.93617021276596</v>
+        <v>97.77777777777777</v>
       </c>
       <c r="F10" t="n">
-        <v>98.93617021276596</v>
+        <v>97.77777777777777</v>
       </c>
       <c r="G10" t="n">
-        <v>23.40425531914894</v>
+        <v>25.55555555555555</v>
       </c>
     </row>
     <row r="11">
@@ -824,22 +824,22 @@
         <v>2017</v>
       </c>
       <c r="B11" t="n">
-        <v>99.16666666666667</v>
+        <v>99.12280701754386</v>
       </c>
       <c r="C11" t="n">
-        <v>96.66666666666667</v>
+        <v>99.12280701754386</v>
       </c>
       <c r="D11" t="n">
-        <v>99.16666666666667</v>
+        <v>99.12280701754386</v>
       </c>
       <c r="E11" t="n">
-        <v>100</v>
+        <v>98.24561403508771</v>
       </c>
       <c r="F11" t="n">
-        <v>100</v>
+        <v>98.24561403508771</v>
       </c>
       <c r="G11" t="n">
-        <v>10.83333333333333</v>
+        <v>13.1578947368421</v>
       </c>
     </row>
     <row r="12">
@@ -847,22 +847,22 @@
         <v>2018</v>
       </c>
       <c r="B12" t="n">
-        <v>98.90109890109891</v>
+        <v>95.45454545454545</v>
       </c>
       <c r="C12" t="n">
-        <v>98.90109890109891</v>
+        <v>97.72727272727273</v>
       </c>
       <c r="D12" t="n">
-        <v>98.90109890109891</v>
+        <v>97.72727272727273</v>
       </c>
       <c r="E12" t="n">
-        <v>98.90109890109891</v>
+        <v>95.45454545454545</v>
       </c>
       <c r="F12" t="n">
-        <v>100</v>
+        <v>97.72727272727273</v>
       </c>
       <c r="G12" t="n">
-        <v>14.28571428571428</v>
+        <v>14.77272727272727</v>
       </c>
     </row>
     <row r="13">
@@ -870,22 +870,22 @@
         <v>2019</v>
       </c>
       <c r="B13" t="n">
-        <v>99.1869918699187</v>
+        <v>100</v>
       </c>
       <c r="C13" t="n">
-        <v>100</v>
+        <v>99.1304347826087</v>
       </c>
       <c r="D13" t="n">
-        <v>98.3739837398374</v>
+        <v>99.1304347826087</v>
       </c>
       <c r="E13" t="n">
-        <v>100</v>
+        <v>98.26086956521739</v>
       </c>
       <c r="F13" t="n">
-        <v>99.1869918699187</v>
+        <v>98.26086956521739</v>
       </c>
       <c r="G13" t="n">
-        <v>13.82113821138211</v>
+        <v>17.39130434782609</v>
       </c>
     </row>
     <row r="14">
@@ -893,22 +893,22 @@
         <v>2020</v>
       </c>
       <c r="B14" t="n">
-        <v>100</v>
+        <v>96.15384615384616</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>98.71794871794873</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>98.71794871794873</v>
       </c>
       <c r="E14" t="n">
-        <v>100</v>
+        <v>98.71794871794873</v>
       </c>
       <c r="F14" t="n">
-        <v>100</v>
+        <v>98.71794871794873</v>
       </c>
       <c r="G14" t="n">
-        <v>26.74418604651163</v>
+        <v>19.23076923076923</v>
       </c>
     </row>
     <row r="15">
@@ -922,16 +922,16 @@
         <v>100</v>
       </c>
       <c r="D15" t="n">
-        <v>100</v>
+        <v>99.26470588235294</v>
       </c>
       <c r="E15" t="n">
         <v>100</v>
       </c>
       <c r="F15" t="n">
-        <v>100</v>
+        <v>98.52941176470588</v>
       </c>
       <c r="G15" t="n">
-        <v>42.46575342465754</v>
+        <v>45.58823529411764</v>
       </c>
     </row>
     <row r="16">
@@ -939,10 +939,10 @@
         <v>2022</v>
       </c>
       <c r="B16" t="n">
-        <v>97.95918367346938</v>
+        <v>96.73913043478261</v>
       </c>
       <c r="C16" t="n">
-        <v>98.9795918367347</v>
+        <v>100</v>
       </c>
       <c r="D16" t="n">
         <v>100</v>
@@ -954,7 +954,7 @@
         <v>100</v>
       </c>
       <c r="G16" t="n">
-        <v>39.79591836734694</v>
+        <v>43.47826086956522</v>
       </c>
     </row>
     <row r="17">
@@ -962,7 +962,7 @@
         <v>2023</v>
       </c>
       <c r="B17" t="n">
-        <v>99.03846153846155</v>
+        <v>98.98989898989899</v>
       </c>
       <c r="C17" t="n">
         <v>100</v>
@@ -971,13 +971,13 @@
         <v>100</v>
       </c>
       <c r="E17" t="n">
-        <v>100</v>
+        <v>97.97979797979798</v>
       </c>
       <c r="F17" t="n">
-        <v>100</v>
+        <v>97.97979797979798</v>
       </c>
       <c r="G17" t="n">
-        <v>43.26923076923077</v>
+        <v>48.48484848484848</v>
       </c>
     </row>
     <row r="18">
@@ -985,22 +985,22 @@
         <v>2024</v>
       </c>
       <c r="B18" t="n">
-        <v>97.22222222222221</v>
+        <v>100</v>
       </c>
       <c r="C18" t="n">
-        <v>97.91666666666666</v>
+        <v>100</v>
       </c>
       <c r="D18" t="n">
-        <v>97.91666666666666</v>
+        <v>100</v>
       </c>
       <c r="E18" t="n">
-        <v>100</v>
+        <v>99.24812030075188</v>
       </c>
       <c r="F18" t="n">
-        <v>100</v>
+        <v>98.49624060150376</v>
       </c>
       <c r="G18" t="n">
-        <v>38.19444444444444</v>
+        <v>43.60902255639098</v>
       </c>
     </row>
     <row r="19">
@@ -1017,13 +1017,13 @@
         <v>100</v>
       </c>
       <c r="E19" t="n">
-        <v>100</v>
+        <v>96.7741935483871</v>
       </c>
       <c r="F19" t="n">
         <v>100</v>
       </c>
       <c r="G19" t="n">
-        <v>32.25806451612903</v>
+        <v>58.06451612903226</v>
       </c>
     </row>
     <row r="20">
